--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013870</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013846</v>
+        <v>127013852</v>
       </c>
       <c r="B3" t="n">
         <v>57657</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505180</v>
+        <v>505369</v>
       </c>
       <c r="R3" t="n">
-        <v>7142830</v>
+        <v>7142954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013868</v>
+        <v>127013846</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505340</v>
+        <v>505180</v>
       </c>
       <c r="R4" t="n">
-        <v>7142736</v>
+        <v>7142830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013871</v>
+        <v>127013868</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505361</v>
+        <v>505340</v>
       </c>
       <c r="R5" t="n">
-        <v>7142709</v>
+        <v>7142736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013852</v>
+        <v>127013871</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505369</v>
+        <v>505361</v>
       </c>
       <c r="R6" t="n">
-        <v>7142954</v>
+        <v>7142709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>127013872</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127013862</v>
       </c>
       <c r="B8" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127013860</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127013877</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013847</v>
+        <v>127013865</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505116</v>
+        <v>505253</v>
       </c>
       <c r="R12" t="n">
-        <v>7142892</v>
+        <v>7142888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013865</v>
+        <v>127013847</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505253</v>
+        <v>505116</v>
       </c>
       <c r="R13" t="n">
-        <v>7142888</v>
+        <v>7142892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,7 +1867,7 @@
         <v>127013859</v>
       </c>
       <c r="B14" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>127013858</v>
       </c>
       <c r="B15" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127013866</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>127013864</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>127013867</v>
       </c>
       <c r="B18" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013870</v>
       </c>
       <c r="B2" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127013868</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127013871</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127013872</v>
       </c>
       <c r="B7" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127013862</v>
       </c>
       <c r="B8" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127013860</v>
       </c>
       <c r="B9" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127013877</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127013865</v>
       </c>
       <c r="B12" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>127013859</v>
       </c>
       <c r="B14" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>127013858</v>
       </c>
       <c r="B15" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127013866</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>127013864</v>
       </c>
       <c r="B17" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>127013867</v>
       </c>
       <c r="B18" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013852</v>
+        <v>127013868</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505369</v>
+        <v>505340</v>
       </c>
       <c r="R3" t="n">
-        <v>7142954</v>
+        <v>7142736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013846</v>
+        <v>127013871</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505180</v>
+        <v>505361</v>
       </c>
       <c r="R4" t="n">
-        <v>7142830</v>
+        <v>7142709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013868</v>
+        <v>127013852</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505340</v>
+        <v>505369</v>
       </c>
       <c r="R5" t="n">
-        <v>7142736</v>
+        <v>7142954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013871</v>
+        <v>127013846</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505361</v>
+        <v>505180</v>
       </c>
       <c r="R6" t="n">
-        <v>7142709</v>
+        <v>7142830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013860</v>
+        <v>127013877</v>
       </c>
       <c r="B9" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R9" t="n">
-        <v>7142738</v>
+        <v>7142651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013877</v>
+        <v>127013860</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R10" t="n">
-        <v>7142651</v>
+        <v>7142738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013865</v>
+        <v>127013847</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505253</v>
+        <v>505116</v>
       </c>
       <c r="R12" t="n">
-        <v>7142888</v>
+        <v>7142892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1736,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013847</v>
+        <v>127013865</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505116</v>
+        <v>505253</v>
       </c>
       <c r="R13" t="n">
-        <v>7142892</v>
+        <v>7142888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,11 +1838,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013847</v>
+        <v>127013865</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505116</v>
+        <v>505253</v>
       </c>
       <c r="R12" t="n">
-        <v>7142892</v>
+        <v>7142888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013865</v>
+        <v>127013847</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505253</v>
+        <v>505116</v>
       </c>
       <c r="R13" t="n">
-        <v>7142888</v>
+        <v>7142892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013868</v>
+        <v>127013852</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505340</v>
+        <v>505369</v>
       </c>
       <c r="R3" t="n">
-        <v>7142736</v>
+        <v>7142954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013871</v>
+        <v>127013846</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505361</v>
+        <v>505180</v>
       </c>
       <c r="R4" t="n">
-        <v>7142709</v>
+        <v>7142830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013852</v>
+        <v>127013868</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505369</v>
+        <v>505340</v>
       </c>
       <c r="R5" t="n">
-        <v>7142954</v>
+        <v>7142736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013846</v>
+        <v>127013871</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505180</v>
+        <v>505361</v>
       </c>
       <c r="R6" t="n">
-        <v>7142830</v>
+        <v>7142709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013852</v>
+        <v>127013868</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505369</v>
+        <v>505340</v>
       </c>
       <c r="R3" t="n">
-        <v>7142954</v>
+        <v>7142736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013846</v>
+        <v>127013871</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505180</v>
+        <v>505361</v>
       </c>
       <c r="R4" t="n">
-        <v>7142830</v>
+        <v>7142709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013868</v>
+        <v>127013852</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505340</v>
+        <v>505369</v>
       </c>
       <c r="R5" t="n">
-        <v>7142736</v>
+        <v>7142954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013871</v>
+        <v>127013846</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505361</v>
+        <v>505180</v>
       </c>
       <c r="R6" t="n">
-        <v>7142709</v>
+        <v>7142830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013877</v>
+        <v>127013860</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R9" t="n">
-        <v>7142651</v>
+        <v>7142738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013860</v>
+        <v>127013877</v>
       </c>
       <c r="B10" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R10" t="n">
-        <v>7142738</v>
+        <v>7142651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013852</v>
+        <v>127013872</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505369</v>
+        <v>505342</v>
       </c>
       <c r="R5" t="n">
-        <v>7142954</v>
+        <v>7142655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013846</v>
+        <v>127013862</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>80118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505180</v>
+        <v>505342</v>
       </c>
       <c r="R6" t="n">
-        <v>7142830</v>
+        <v>7142655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013872</v>
+        <v>127013860</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,7 +1198,7 @@
         <v>505342</v>
       </c>
       <c r="R7" t="n">
-        <v>7142655</v>
+        <v>7142738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013862</v>
+        <v>127013877</v>
       </c>
       <c r="B8" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R8" t="n">
-        <v>7142655</v>
+        <v>7142651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013860</v>
+        <v>127013865</v>
       </c>
       <c r="B9" t="n">
-        <v>80118</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505342</v>
+        <v>505253</v>
       </c>
       <c r="R9" t="n">
-        <v>7142738</v>
+        <v>7142888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013877</v>
+        <v>127013859</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505327</v>
+        <v>505367</v>
       </c>
       <c r="R10" t="n">
-        <v>7142651</v>
+        <v>7142953</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127013853</v>
+        <v>127013858</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>80118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505376</v>
+        <v>505189</v>
       </c>
       <c r="R11" t="n">
-        <v>7142944</v>
+        <v>7142986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1624,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013865</v>
+        <v>127013866</v>
       </c>
       <c r="B12" t="n">
         <v>80117</v>
@@ -1700,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505253</v>
+        <v>505310</v>
       </c>
       <c r="R12" t="n">
-        <v>7142888</v>
+        <v>7142943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013847</v>
+        <v>127013864</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505116</v>
+        <v>505189</v>
       </c>
       <c r="R13" t="n">
-        <v>7142892</v>
+        <v>7142986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,11 +1818,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013859</v>
+        <v>127013867</v>
       </c>
       <c r="B14" t="n">
-        <v>80118</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1961,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013858</v>
+        <v>127013846</v>
       </c>
       <c r="B15" t="n">
-        <v>80118</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505189</v>
+        <v>505180</v>
       </c>
       <c r="R15" t="n">
-        <v>7142986</v>
+        <v>7142830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2032,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013866</v>
+        <v>127013852</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505310</v>
+        <v>505369</v>
       </c>
       <c r="R16" t="n">
-        <v>7142943</v>
+        <v>7142954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127013864</v>
+        <v>127013853</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505189</v>
+        <v>505376</v>
       </c>
       <c r="R17" t="n">
-        <v>7142986</v>
+        <v>7142944</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2226,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127013867</v>
+        <v>127013847</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505367</v>
+        <v>505116</v>
       </c>
       <c r="R18" t="n">
-        <v>7142953</v>
+        <v>7142892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013870</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127013868</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127013871</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127013872</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127013862</v>
       </c>
       <c r="B6" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127013860</v>
       </c>
       <c r="B7" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127013877</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127013865</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127013859</v>
       </c>
       <c r="B10" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>127013858</v>
       </c>
       <c r="B11" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>127013866</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127013864</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>127013867</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013846</v>
+        <v>127013852</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505180</v>
+        <v>505369</v>
       </c>
       <c r="R15" t="n">
-        <v>7142830</v>
+        <v>7142954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013852</v>
+        <v>127013846</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505369</v>
+        <v>505180</v>
       </c>
       <c r="R16" t="n">
-        <v>7142954</v>
+        <v>7142830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2148,7 +2148,7 @@
         <v>127013853</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127013847</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013860</v>
+        <v>127013877</v>
       </c>
       <c r="B7" t="n">
-        <v>80122</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R7" t="n">
-        <v>7142738</v>
+        <v>7142651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013877</v>
+        <v>127013860</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>80122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R8" t="n">
-        <v>7142651</v>
+        <v>7142738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013852</v>
+        <v>127013846</v>
       </c>
       <c r="B15" t="n">
         <v>57661</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505369</v>
+        <v>505180</v>
       </c>
       <c r="R15" t="n">
-        <v>7142954</v>
+        <v>7142830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013846</v>
+        <v>127013852</v>
       </c>
       <c r="B16" t="n">
         <v>57661</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505180</v>
+        <v>505369</v>
       </c>
       <c r="R16" t="n">
-        <v>7142830</v>
+        <v>7142954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013846</v>
+        <v>127013852</v>
       </c>
       <c r="B15" t="n">
         <v>57661</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505180</v>
+        <v>505369</v>
       </c>
       <c r="R15" t="n">
-        <v>7142830</v>
+        <v>7142954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013852</v>
+        <v>127013846</v>
       </c>
       <c r="B16" t="n">
         <v>57661</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505369</v>
+        <v>505180</v>
       </c>
       <c r="R16" t="n">
-        <v>7142954</v>
+        <v>7142830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013870</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127013868</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127013871</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127013872</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127013862</v>
       </c>
       <c r="B6" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013877</v>
+        <v>127013860</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R7" t="n">
-        <v>7142651</v>
+        <v>7142738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013860</v>
+        <v>127013877</v>
       </c>
       <c r="B8" t="n">
-        <v>80122</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R8" t="n">
-        <v>7142738</v>
+        <v>7142651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,7 +1362,7 @@
         <v>127013865</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127013859</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>127013858</v>
       </c>
       <c r="B11" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>127013866</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127013864</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>127013867</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127013852</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>127013846</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127013853</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127013847</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013868</v>
+        <v>127013871</v>
       </c>
       <c r="B3" t="n">
         <v>80123</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505340</v>
+        <v>505361</v>
       </c>
       <c r="R3" t="n">
-        <v>7142736</v>
+        <v>7142709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013871</v>
+        <v>127013868</v>
       </c>
       <c r="B4" t="n">
         <v>80123</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505361</v>
+        <v>505340</v>
       </c>
       <c r="R4" t="n">
-        <v>7142709</v>
+        <v>7142736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013860</v>
+        <v>127013877</v>
       </c>
       <c r="B7" t="n">
-        <v>80124</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R7" t="n">
-        <v>7142738</v>
+        <v>7142651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013877</v>
+        <v>127013860</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>80124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R8" t="n">
-        <v>7142651</v>
+        <v>7142738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013871</v>
+        <v>127013868</v>
       </c>
       <c r="B3" t="n">
         <v>80123</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505361</v>
+        <v>505340</v>
       </c>
       <c r="R3" t="n">
-        <v>7142709</v>
+        <v>7142736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013868</v>
+        <v>127013871</v>
       </c>
       <c r="B4" t="n">
         <v>80123</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505340</v>
+        <v>505361</v>
       </c>
       <c r="R4" t="n">
-        <v>7142736</v>
+        <v>7142709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013877</v>
+        <v>127013860</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>80124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R7" t="n">
-        <v>7142651</v>
+        <v>7142738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013860</v>
+        <v>127013877</v>
       </c>
       <c r="B8" t="n">
-        <v>80124</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505342</v>
+        <v>505327</v>
       </c>
       <c r="R8" t="n">
-        <v>7142738</v>
+        <v>7142651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013852</v>
+        <v>127013846</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505369</v>
+        <v>505180</v>
       </c>
       <c r="R15" t="n">
-        <v>7142954</v>
+        <v>7142830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013846</v>
+        <v>127013852</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505180</v>
+        <v>505369</v>
       </c>
       <c r="R16" t="n">
-        <v>7142830</v>
+        <v>7142954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2148,7 +2148,7 @@
         <v>127013853</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127013847</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013846</v>
+        <v>127013852</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505180</v>
+        <v>505369</v>
       </c>
       <c r="R15" t="n">
-        <v>7142830</v>
+        <v>7142954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013852</v>
+        <v>127013846</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505369</v>
+        <v>505180</v>
       </c>
       <c r="R16" t="n">
-        <v>7142954</v>
+        <v>7142830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2148,7 +2148,7 @@
         <v>127013853</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127013847</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26299-2025 artfynd.xlsx
+++ b/artfynd/A 26299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013870</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013868</v>
+        <v>127013852</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505340</v>
+        <v>505369</v>
       </c>
       <c r="R3" t="n">
-        <v>7142736</v>
+        <v>7142954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013871</v>
+        <v>127013846</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505361</v>
+        <v>505180</v>
       </c>
       <c r="R4" t="n">
-        <v>7142709</v>
+        <v>7142830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013872</v>
+        <v>127013868</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505342</v>
+        <v>505340</v>
       </c>
       <c r="R5" t="n">
-        <v>7142655</v>
+        <v>7142736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013862</v>
+        <v>127013871</v>
       </c>
       <c r="B6" t="n">
-        <v>80124</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505342</v>
+        <v>505361</v>
       </c>
       <c r="R6" t="n">
-        <v>7142655</v>
+        <v>7142709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013860</v>
+        <v>127013872</v>
       </c>
       <c r="B7" t="n">
-        <v>80124</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1198,7 +1208,7 @@
         <v>505342</v>
       </c>
       <c r="R7" t="n">
-        <v>7142738</v>
+        <v>7142655</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013877</v>
+        <v>127013862</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>80115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505327</v>
+        <v>505342</v>
       </c>
       <c r="R8" t="n">
-        <v>7142651</v>
+        <v>7142655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1328,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013865</v>
+        <v>127013860</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505253</v>
+        <v>505342</v>
       </c>
       <c r="R9" t="n">
-        <v>7142888</v>
+        <v>7142738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013859</v>
+        <v>127013877</v>
       </c>
       <c r="B10" t="n">
-        <v>80124</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505367</v>
+        <v>505327</v>
       </c>
       <c r="R10" t="n">
-        <v>7142953</v>
+        <v>7142651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1553,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127013858</v>
+        <v>127013853</v>
       </c>
       <c r="B11" t="n">
-        <v>80124</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505189</v>
+        <v>505376</v>
       </c>
       <c r="R11" t="n">
-        <v>7142986</v>
+        <v>7142944</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1624,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013866</v>
+        <v>127013865</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505310</v>
+        <v>505253</v>
       </c>
       <c r="R12" t="n">
-        <v>7142943</v>
+        <v>7142888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013864</v>
+        <v>127013847</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505189</v>
+        <v>505116</v>
       </c>
       <c r="R13" t="n">
-        <v>7142986</v>
+        <v>7142892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1818,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013867</v>
+        <v>127013859</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>80115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1941,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013852</v>
+        <v>127013858</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>80115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505369</v>
+        <v>505189</v>
       </c>
       <c r="R15" t="n">
-        <v>7142954</v>
+        <v>7142986</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,11 +2032,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013846</v>
+        <v>127013866</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505180</v>
+        <v>505310</v>
       </c>
       <c r="R16" t="n">
-        <v>7142830</v>
+        <v>7142943</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gammalt bohål ca 4 m upp i granrötad o knäckt gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127013853</v>
+        <v>127013864</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>80114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505376</v>
+        <v>505189</v>
       </c>
       <c r="R17" t="n">
-        <v>7142944</v>
+        <v>7142986</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,11 +2226,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127013847</v>
+        <v>127013867</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>80114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505116</v>
+        <v>505367</v>
       </c>
       <c r="R18" t="n">
-        <v>7142892</v>
+        <v>7142953</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
